--- a/data/trans_orig/P57C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha sido optimista respecto a su futuro en 2023</t>
+          <t>Población según si ha sido optimista respecto a su futuro en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2415</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>464</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36021</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>51647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51820</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41846</t>
+          <t>41709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63356</t>
+          <t>63337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75721</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107714</t>
+          <t>108868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205872</t>
+          <t>205591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241520</t>
+          <t>241642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173667</t>
+          <t>171736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202085</t>
+          <t>203004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389638</t>
+          <t>389547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>435089</t>
+          <t>437213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>48928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41025</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52825</t>
+          <t>52710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>81913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1412,97 +1412,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2287</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6965</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2287</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7173</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57631</t>
+          <t>56078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>37619</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60921</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66849</t>
+          <t>68228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105380</t>
+          <t>106639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242410</t>
+          <t>242438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299270</t>
+          <t>304975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>280096</t>
+          <t>279925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319874</t>
+          <t>319459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>534286</t>
+          <t>533377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>608581</t>
+          <t>605861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,0%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172924</t>
+          <t>166793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230215</t>
+          <t>228465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168396</t>
+          <t>169368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>317438</t>
+          <t>315226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>383701</t>
+          <t>387544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42641</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>36295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61027</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39899</t>
+          <t>39878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63563</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48975</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>73021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95844</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131356</t>
+          <t>128816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76865</t>
+          <t>77753</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>109705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86894</t>
+          <t>86231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114124</t>
+          <t>113191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171327</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>214222</t>
+          <t>213945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115864</t>
+          <t>114664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151760</t>
+          <t>150109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126227</t>
+          <t>127283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157981</t>
+          <t>159005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250194</t>
+          <t>249073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298187</t>
+          <t>298129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>43982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37097</t>
+          <t>39109</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81015</t>
+          <t>77877</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137401</t>
+          <t>135450</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>57736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91232</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207930</t>
+          <t>204516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164078</t>
+          <t>164504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>293633</t>
+          <t>283925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142336</t>
+          <t>141723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187253</t>
+          <t>185130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>179761</t>
+          <t>181909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>319908</t>
+          <t>325380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>339219</t>
+          <t>342845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>509022</t>
+          <t>498703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>407</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124952</t>
+          <t>125597</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145611</t>
+          <t>145727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157112</t>
+          <t>156197</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>174016</t>
+          <t>173694</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>289267</t>
+          <t>288441</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>314664</t>
+          <t>314771</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>28665</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57010</t>
+          <t>57616</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>41245</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35294</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>71063</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>38742</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>56662</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>80891</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>107475</t>
+          <t>110410</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>71717</t>
+          <t>72016</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>100005</t>
+          <t>99612</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>68270</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>92111</t>
+          <t>91829</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>146958</t>
+          <t>145559</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>183576</t>
+          <t>181957</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>78052</t>
+          <t>80762</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>109563</t>
+          <t>110733</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>94694</t>
+          <t>94308</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>156750</t>
+          <t>158724</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>195927</t>
+          <t>197835</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>33014</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>62745</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>102336</t>
+          <t>103347</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78452</t>
+          <t>82197</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>160313</t>
+          <t>161067</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>256083</t>
+          <t>251899</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>311952</t>
+          <t>311714</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>357570</t>
+          <t>360701</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>695834</t>
+          <t>665186</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>646609</t>
+          <t>642773</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1072766</t>
+          <t>1016572</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>222731</t>
+          <t>221944</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>279067</t>
+          <t>282158</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>339669</t>
+          <t>337284</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>284760</t>
+          <t>318118</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>593050</t>
+          <t>596738</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>23255</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>75923</t>
+          <t>77565</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>75852</t>
+          <t>74460</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>103447</t>
+          <t>101850</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>87700</t>
+          <t>84935</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>173426</t>
+          <t>173274</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>51222</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>164811</t>
+          <t>168447</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>146382</t>
+          <t>146164</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>182324</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>175008</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>338123</t>
+          <t>340504</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>134309</t>
+          <t>136004</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>420464</t>
+          <t>420052</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>246771</t>
+          <t>247733</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>290404</t>
+          <t>290160</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>348668</t>
+          <t>359706</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>681493</t>
+          <t>684529</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>262970</t>
+          <t>263079</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>713598</t>
+          <t>706787</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>161801</t>
+          <t>165410</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>207525</t>
+          <t>207490</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>442112</t>
+          <t>441230</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1012189</t>
+          <t>1013946</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>82600</t>
+          <t>83137</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>124827</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>175927</t>
+          <t>179840</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>126441</t>
+          <t>126789</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>193993</t>
+          <t>192566</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>181360</t>
+          <t>183988</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>257403</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>332625</t>
+          <t>338427</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>432127</t>
+          <t>435654</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>316511</t>
+          <t>311671</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>454903</t>
+          <t>452641</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>421735</t>
+          <t>414207</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>571656</t>
+          <t>572000</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>796888</t>
+          <t>816696</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>999056</t>
+          <t>1004693</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1160894</t>
+          <t>1150978</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1611729</t>
+          <t>1609754</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1576924</t>
+          <t>1583768</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2104043</t>
+          <t>2136869</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2882394</t>
+          <t>2898143</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3524172</t>
+          <t>3529577</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1166794</t>
+          <t>1164569</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1807822</t>
+          <t>1794774</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>911991</t>
+          <t>925272</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1240325</t>
+          <t>1232117</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2183899</t>
+          <t>2188436</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2959149</t>
+          <t>2952345</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>477</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51647</t>
+          <t>41450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>52824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>55790</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63337</t>
+          <t>67016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>90929</t>
+          <t>96310</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75971</t>
+          <t>81359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108868</t>
+          <t>111531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>224546</t>
+          <t>223759</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205591</t>
+          <t>207241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241642</t>
+          <t>238762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>189051</t>
+          <t>202214</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171736</t>
+          <t>187336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203004</t>
+          <t>215284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>413596</t>
+          <t>425973</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389547</t>
+          <t>403221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>437213</t>
+          <t>446219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -1177,102 +1177,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34564</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>54119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>16,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>41345</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32569</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53855</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>82702</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>69118</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>99761</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>15,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>31240</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>24310</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40670</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>65804</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>52710</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>81913</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56078</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>39971</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59808</t>
+          <t>64107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>85385</t>
+          <t>88066</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68228</t>
+          <t>70802</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106639</t>
+          <t>108764</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>271496</t>
+          <t>279010</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242438</t>
+          <t>246214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304975</t>
+          <t>304739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>300107</t>
+          <t>317126</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>279925</t>
+          <t>294949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319459</t>
+          <t>336941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>571603</t>
+          <t>596136</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>533377</t>
+          <t>557838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>605861</t>
+          <t>630707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>198631</t>
+          <t>203118</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166793</t>
+          <t>178195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228465</t>
+          <t>232458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>161366</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>142994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169368</t>
+          <t>183764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>348536</t>
+          <t>364484</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315226</t>
+          <t>329890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387544</t>
+          <t>397949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>509500</t>
+          <t>540798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>509500</t>
+          <t>540798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>509500</t>
+          <t>540798</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1026893</t>
+          <t>1070457</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1026893</t>
+          <t>1070457</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1026893</t>
+          <t>1070457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24574</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36295</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>49769</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59786</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51159</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39878</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>65517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59951</t>
+          <t>63665</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48852</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>75042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>111110</t>
+          <t>116811</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95468</t>
+          <t>101708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128816</t>
+          <t>135134</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>93163</t>
+          <t>91736</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77753</t>
+          <t>78497</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109705</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>103732</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86231</t>
+          <t>90500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113191</t>
+          <t>118159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>193063</t>
+          <t>195469</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171894</t>
+          <t>174769</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213945</t>
+          <t>215631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>132775</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114664</t>
+          <t>112595</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150109</t>
+          <t>147754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>142013</t>
+          <t>140605</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127283</t>
+          <t>125616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159005</t>
+          <t>158666</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>274789</t>
+          <t>271578</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249073</t>
+          <t>248651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298129</t>
+          <t>296075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>313846</t>
+          <t>313916</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313846</t>
+          <t>313916</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>313846</t>
+          <t>313916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>346752</t>
+          <t>353953</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>346752</t>
+          <t>353953</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>346752</t>
+          <t>353953</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>660599</t>
+          <t>667869</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>660599</t>
+          <t>667869</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>660599</t>
+          <t>667869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>45940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>50599</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62013</t>
+          <t>68715</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39109</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80842</t>
+          <t>82446</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112612</t>
+          <t>127483</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77877</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>135450</t>
+          <t>151058</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>76447</t>
+          <t>82058</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>64856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95779</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>136484</t>
+          <t>117337</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>100285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204516</t>
+          <t>134609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>212931</t>
+          <t>199395</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164504</t>
+          <t>174179</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283925</t>
+          <t>226730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>163873</t>
+          <t>208467</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>141723</t>
+          <t>183439</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>185130</t>
+          <t>231482</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>236736</t>
+          <t>190952</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181909</t>
+          <t>171015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>325380</t>
+          <t>211375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>400608</t>
+          <t>399419</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>342845</t>
+          <t>365134</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>498703</t>
+          <t>430345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311206</t>
+          <t>371676</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>311206</t>
+          <t>371676</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311206</t>
+          <t>371676</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>474426</t>
+          <t>419104</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>474426</t>
+          <t>419104</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>474426</t>
+          <t>419104</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>785631</t>
+          <t>790781</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>785631</t>
+          <t>790781</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>785631</t>
+          <t>790781</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,22 +3523,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>135956</t>
+          <t>154750</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>125597</t>
+          <t>142740</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145727</t>
+          <t>164912</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>166168</t>
+          <t>180884</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156197</t>
+          <t>170250</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>188961</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>302124</t>
+          <t>335634</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>288441</t>
+          <t>320426</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>314771</t>
+          <t>349908</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>41729</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57616</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>43969</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4248,27 +4248,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>41417</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>28199</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>49175</t>
+          <t>51180</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>72839</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>47475</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>58528</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>49552</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>56662</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>93177</t>
+          <t>97027</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>80891</t>
+          <t>82321</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>110410</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>86659</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>72016</t>
+          <t>72934</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>99612</t>
+          <t>101769</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>78955</t>
+          <t>81635</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>70563</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>91829</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>163952</t>
+          <t>168294</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>150178</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>181957</t>
+          <t>186845</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>94865</t>
+          <t>90618</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>80762</t>
+          <t>75565</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>110733</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>82185</t>
+          <t>83113</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>94308</t>
+          <t>96265</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>177050</t>
+          <t>173730</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>154869</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>197835</t>
+          <t>194459</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>25689</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>41168</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4930,22 +4930,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32155</t>
+          <t>36064</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>47333</t>
+          <t>57879</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>74621</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>61531</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>82546</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>72931</t>
+          <t>82751</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>103347</t>
+          <t>98954</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>127932</t>
+          <t>144283</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>82197</t>
+          <t>122268</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>161067</t>
+          <t>171269</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>284646</t>
+          <t>328886</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>251899</t>
+          <t>299335</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>311714</t>
+          <t>359686</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>485853</t>
+          <t>333245</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>360701</t>
+          <t>306230</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>665186</t>
+          <t>358078</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>770498</t>
+          <t>662130</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>642773</t>
+          <t>624544</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1016572</t>
+          <t>701207</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>250405</t>
+          <t>292025</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>221944</t>
+          <t>261209</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>282158</t>
+          <t>319150</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>248933</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>124258</t>
+          <t>279423</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>337284</t>
+          <t>329481</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>499338</t>
+          <t>595539</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>318118</t>
+          <t>555480</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>596738</t>
+          <t>634946</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>623532</t>
+          <t>718813</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>623532</t>
+          <t>718813</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>623532</t>
+          <t>718813</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>847831</t>
+          <t>769921</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>847831</t>
+          <t>769921</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>847831</t>
+          <t>769921</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1471363</t>
+          <t>1488734</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1471363</t>
+          <t>1488734</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1471363</t>
+          <t>1488734</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>28749</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>40600</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>52408</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>45095</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>77565</t>
+          <t>74635</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>88502</t>
+          <t>101412</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>74460</t>
+          <t>86696</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>101850</t>
+          <t>119036</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>140909</t>
+          <t>159064</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>139097</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>173274</t>
+          <t>182743</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>133042</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>113023</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>168447</t>
+          <t>154286</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>164174</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>146164</t>
+          <t>170925</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>182324</t>
+          <t>215120</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>280382</t>
+          <t>325272</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>175008</t>
+          <t>297016</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>340504</t>
+          <t>356392</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>301482</t>
+          <t>350427</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>136004</t>
+          <t>318071</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>420052</t>
+          <t>380081</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>269646</t>
+          <t>317772</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>247733</t>
+          <t>291217</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>290160</t>
+          <t>343692</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>571128</t>
+          <t>668199</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>359706</t>
+          <t>626848</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>684529</t>
+          <t>705958</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>242327</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>263079</t>
+          <t>213445</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>706787</t>
+          <t>274084</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>183338</t>
+          <t>205179</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>165410</t>
+          <t>183439</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>207490</t>
+          <t>230885</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>630108</t>
+          <t>447506</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>441230</t>
+          <t>411370</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1013946</t>
+          <t>488771</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>83569</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>65137</t>
+          <t>75545</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>101700</t>
+          <t>108369</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>124827</t>
+          <t>142048</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>179840</t>
+          <t>188852</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>126789</t>
+          <t>151211</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>192566</t>
+          <t>198556</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>226484</t>
+          <t>251908</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>183988</t>
+          <t>227786</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>257403</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>391753</t>
+          <t>426361</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>338427</t>
+          <t>389884</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>435654</t>
+          <t>460634</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>404447</t>
+          <t>442512</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>311671</t>
+          <t>406330</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>452641</t>
+          <t>484479</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>520189</t>
+          <t>577978</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>414207</t>
+          <t>540352</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>572000</t>
+          <t>619720</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>924636</t>
+          <t>1020490</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>816696</t>
+          <t>967213</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1004693</t>
+          <t>1081329</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1472734</t>
+          <t>1597285</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1150978</t>
+          <t>1537246</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1609754</t>
+          <t>1665747</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1726162</t>
+          <t>1653945</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1583768</t>
+          <t>1603071</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2136869</t>
+          <t>1708570</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>3198895</t>
+          <t>3251230</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2898143</t>
+          <t>3173730</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3529577</t>
+          <t>3337507</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1346795</t>
+          <t>1240767</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1164569</t>
+          <t>1181856</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1794774</t>
+          <t>1302138</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1094259</t>
+          <t>1147268</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>925272</t>
+          <t>1096127</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1232117</t>
+          <t>1203147</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2441053</t>
+          <t>2388036</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2188436</t>
+          <t>2300544</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2952345</t>
+          <t>2471910</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
